--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N63_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N63_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>80.36489737427628</v>
+        <v>13.0592958233199</v>
       </c>
       <c r="D2" t="n">
-        <v>83.24069431275427</v>
+        <v>13.52661282582257</v>
       </c>
       <c r="E2" t="n">
-        <v>25.52754631353907</v>
+        <v>4.148226275950099</v>
       </c>
       <c r="F2" t="n">
-        <v>26.87305282275615</v>
+        <v>4.366871083697875</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.89620600570753</v>
+        <v>10.54563347592747</v>
       </c>
       <c r="D3" t="n">
-        <v>68.06145786504122</v>
+        <v>11.0599869030692</v>
       </c>
       <c r="E3" t="n">
-        <v>25.52754631353907</v>
+        <v>4.148226275950099</v>
       </c>
       <c r="F3" t="n">
-        <v>26.87305282275615</v>
+        <v>4.366871083697875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.95385817596738</v>
+        <v>5.355001953594699</v>
       </c>
       <c r="D4" t="n">
-        <v>31.8584103666715</v>
+        <v>5.176991684584119</v>
       </c>
       <c r="E4" t="n">
-        <v>25.52754631353907</v>
+        <v>4.148226275950099</v>
       </c>
       <c r="F4" t="n">
-        <v>26.87305282275615</v>
+        <v>4.366871083697875</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.56588877708766</v>
+        <v>3.016956926276745</v>
       </c>
       <c r="D5" t="n">
-        <v>18.57627354973868</v>
+        <v>3.018644451832535</v>
       </c>
       <c r="E5" t="n">
-        <v>25.52754631353907</v>
+        <v>4.148226275950099</v>
       </c>
       <c r="F5" t="n">
-        <v>26.87305282275615</v>
+        <v>4.366871083697875</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.767622306469208</v>
+        <v>1.587238624801246</v>
       </c>
       <c r="D6" t="n">
-        <v>9.920651610155742</v>
+        <v>1.612105886650308</v>
       </c>
       <c r="E6" t="n">
-        <v>25.52754631353907</v>
+        <v>4.148226275950099</v>
       </c>
       <c r="F6" t="n">
-        <v>26.87305282275615</v>
+        <v>4.366871083697875</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.1178949543132</v>
+        <v>3.919157930075895</v>
       </c>
       <c r="D7" t="n">
-        <v>24.23464432782982</v>
+        <v>3.938129703272345</v>
       </c>
       <c r="E7" t="n">
-        <v>25.52754631353907</v>
+        <v>4.148226275950099</v>
       </c>
       <c r="F7" t="n">
-        <v>26.87305282275615</v>
+        <v>4.366871083697875</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
